--- a/data/Potato_database.xlsx
+++ b/data/Potato_database.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="254">
   <si>
     <t>Parameters</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Ideal pH maximum</t>
   </si>
   <si>
-    <t xml:space="preserve">Ideal temprature minimum </t>
+    <t>Ideal temprature minimum</t>
   </si>
   <si>
     <t>ideal temprature maximum</t>
@@ -196,6 +196,30 @@
     <t>image name</t>
   </si>
   <si>
+    <t>fertilizer cost</t>
+  </si>
+  <si>
+    <t>irrigation cost</t>
+  </si>
+  <si>
+    <t>labour cost</t>
+  </si>
+  <si>
+    <t>expected yield</t>
+  </si>
+  <si>
+    <t>market price</t>
+  </si>
+  <si>
+    <t>first irrigation</t>
+  </si>
+  <si>
+    <t>vegetative irrigation</t>
+  </si>
+  <si>
+    <t>last irrigation</t>
+  </si>
+  <si>
     <t>Sante</t>
   </si>
   <si>
@@ -253,9 +277,6 @@
     <t>150-250 kg\ha</t>
   </si>
   <si>
-    <t>2000-2500 kg\ha</t>
-  </si>
-  <si>
     <t>8-10 cm</t>
   </si>
   <si>
@@ -323,6 +344,18 @@
   </si>
   <si>
     <t>sante.jpg</t>
+  </si>
+  <si>
+    <t>2500kg/ha</t>
+  </si>
+  <si>
+    <t>20 days after planting</t>
+  </si>
+  <si>
+    <t>every 7 days</t>
+  </si>
+  <si>
+    <t>10 days before harvest</t>
   </si>
   <si>
     <t>Lady Rosetta</t>
@@ -1917,7 +1950,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BB16"/>
+  <dimension ref="A1:BK16"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="18.2857142857143" customWidth="1"/>
@@ -1971,10 +2004,20 @@
     <col min="50" max="50" width="40.2857142857143" customWidth="1"/>
     <col min="51" max="51" width="36.4285714285714" customWidth="1"/>
     <col min="52" max="52" width="30.5714285714286" customWidth="1"/>
-    <col min="53" max="53" width="51.2857142857143" customWidth="1"/>
+    <col min="53" max="53" width="109.142857142857" customWidth="1"/>
+    <col min="54" max="54" width="15.4285714285714" customWidth="1"/>
+    <col min="55" max="55" width="11.4285714285714" customWidth="1"/>
+    <col min="56" max="56" width="13.5714285714286" customWidth="1"/>
+    <col min="57" max="57" width="14.5714285714286" customWidth="1"/>
+    <col min="58" max="58" width="15.1428571428571" customWidth="1"/>
+    <col min="59" max="59" width="16.7142857142857" customWidth="1"/>
+    <col min="60" max="60" width="16.1428571428571" customWidth="1"/>
+    <col min="61" max="61" width="18.5714285714286" customWidth="1"/>
+    <col min="62" max="62" width="21.4285714285714" customWidth="1"/>
+    <col min="63" max="63" width="25.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54">
+    <row r="1" spans="1:63">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2137,34 +2180,61 @@
       <c r="BB1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:54">
+      <c r="BC1" t="s">
+        <v>22</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:63">
       <c r="B2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K2">
         <v>5</v>
@@ -2173,159 +2243,186 @@
         <v>6.5</v>
       </c>
       <c r="M2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="N2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" t="s">
+        <v>77</v>
+      </c>
+      <c r="T2" t="s">
+        <v>78</v>
+      </c>
+      <c r="U2" t="s">
+        <v>79</v>
+      </c>
+      <c r="V2" t="s">
+        <v>80</v>
+      </c>
+      <c r="W2">
+        <v>2500</v>
+      </c>
+      <c r="X2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BD2">
+        <v>70000</v>
+      </c>
+      <c r="BE2">
+        <v>25000</v>
+      </c>
+      <c r="BF2">
+        <v>50000</v>
+      </c>
+      <c r="BG2">
+        <v>42</v>
+      </c>
+      <c r="BH2">
+        <v>85000</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:63">
+      <c r="B3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" t="s">
         <v>64</v>
       </c>
-      <c r="O2" t="s">
-        <v>65</v>
-      </c>
-      <c r="P2" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="E3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" t="s">
         <v>67</v>
       </c>
-      <c r="R2" t="s">
+      <c r="H3" t="s">
         <v>68</v>
       </c>
-      <c r="S2" t="s">
+      <c r="I3" t="s">
         <v>69</v>
       </c>
-      <c r="T2" t="s">
+      <c r="J3" t="s">
         <v>70</v>
-      </c>
-      <c r="U2" t="s">
-        <v>71</v>
-      </c>
-      <c r="V2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W2" t="s">
-        <v>73</v>
-      </c>
-      <c r="X2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>94</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:54">
-      <c r="B3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" t="s">
-        <v>62</v>
       </c>
       <c r="K3">
         <v>5.2</v>
@@ -2334,159 +2431,186 @@
         <v>6.5</v>
       </c>
       <c r="M3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" t="s">
+        <v>112</v>
+      </c>
+      <c r="P3" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>114</v>
+      </c>
+      <c r="R3" t="s">
+        <v>76</v>
+      </c>
+      <c r="S3" t="s">
+        <v>76</v>
+      </c>
+      <c r="T3" t="s">
+        <v>115</v>
+      </c>
+      <c r="U3" t="s">
+        <v>79</v>
+      </c>
+      <c r="V3" t="s">
+        <v>78</v>
+      </c>
+      <c r="W3">
+        <v>2500</v>
+      </c>
+      <c r="X3" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>130</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BD3">
+        <v>80000</v>
+      </c>
+      <c r="BE3">
+        <v>25000</v>
+      </c>
+      <c r="BF3">
+        <v>50000</v>
+      </c>
+      <c r="BG3">
+        <v>48</v>
+      </c>
+      <c r="BH3">
+        <v>90000</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>105</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>106</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:63">
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" t="s">
         <v>63</v>
       </c>
-      <c r="N3" t="s">
+      <c r="D4" t="s">
         <v>64</v>
       </c>
-      <c r="O3" t="s">
-        <v>101</v>
-      </c>
-      <c r="P3" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>103</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="E4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" t="s">
         <v>68</v>
       </c>
-      <c r="S3" t="s">
-        <v>68</v>
-      </c>
-      <c r="T3" t="s">
-        <v>104</v>
-      </c>
-      <c r="U3" t="s">
-        <v>71</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="I4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" t="s">
         <v>70</v>
-      </c>
-      <c r="W3" t="s">
-        <v>73</v>
-      </c>
-      <c r="X3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>105</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>112</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:54">
-      <c r="B4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4" t="s">
-        <v>62</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -2495,159 +2619,186 @@
         <v>6.5</v>
       </c>
       <c r="M4" t="s">
+        <v>71</v>
+      </c>
+      <c r="N4" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" t="s">
+        <v>112</v>
+      </c>
+      <c r="P4" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>75</v>
+      </c>
+      <c r="R4" t="s">
+        <v>132</v>
+      </c>
+      <c r="S4" t="s">
+        <v>76</v>
+      </c>
+      <c r="T4" t="s">
+        <v>115</v>
+      </c>
+      <c r="U4" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" t="s">
+        <v>78</v>
+      </c>
+      <c r="W4">
+        <v>3500</v>
+      </c>
+      <c r="X4" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>122</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>122</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>142</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>143</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>144</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BD4">
+        <v>70000</v>
+      </c>
+      <c r="BE4">
+        <v>25000</v>
+      </c>
+      <c r="BF4">
+        <v>50000</v>
+      </c>
+      <c r="BG4">
+        <v>50</v>
+      </c>
+      <c r="BH4">
+        <v>80000</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>105</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:63">
+      <c r="B5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" t="s">
         <v>63</v>
       </c>
-      <c r="N4" t="s">
+      <c r="D5" t="s">
         <v>64</v>
       </c>
-      <c r="O4" t="s">
-        <v>101</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" t="s">
         <v>66</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="G5" t="s">
         <v>67</v>
       </c>
-      <c r="R4" t="s">
-        <v>121</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="H5" t="s">
         <v>68</v>
       </c>
-      <c r="T4" t="s">
-        <v>104</v>
-      </c>
-      <c r="U4" t="s">
-        <v>71</v>
-      </c>
-      <c r="V4" t="s">
+      <c r="I5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" t="s">
         <v>70</v>
-      </c>
-      <c r="W4" t="s">
-        <v>73</v>
-      </c>
-      <c r="X4" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>126</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>127</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>128</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>130</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>111</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>111</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>131</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>132</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:54">
-      <c r="B5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" t="s">
-        <v>62</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -2656,159 +2807,186 @@
         <v>6.5</v>
       </c>
       <c r="M5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="N5" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" t="s">
+        <v>112</v>
+      </c>
+      <c r="P5" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>147</v>
+      </c>
+      <c r="R5" t="s">
+        <v>76</v>
+      </c>
+      <c r="S5" t="s">
+        <v>76</v>
+      </c>
+      <c r="T5" t="s">
+        <v>115</v>
+      </c>
+      <c r="U5" t="s">
+        <v>79</v>
+      </c>
+      <c r="V5" t="s">
+        <v>80</v>
+      </c>
+      <c r="W5">
+        <v>3000</v>
+      </c>
+      <c r="X5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>150</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>151</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>140</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>126</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>127</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>152</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>153</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>104</v>
+      </c>
+      <c r="BD5">
+        <v>60000</v>
+      </c>
+      <c r="BE5">
+        <v>25000</v>
+      </c>
+      <c r="BF5">
+        <v>50000</v>
+      </c>
+      <c r="BG5">
+        <v>45</v>
+      </c>
+      <c r="BH5">
+        <v>75000</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>105</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>106</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:63">
+      <c r="B6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" t="s">
         <v>64</v>
       </c>
-      <c r="O5" t="s">
-        <v>101</v>
-      </c>
-      <c r="P5" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>136</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="E6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" t="s">
         <v>68</v>
       </c>
-      <c r="S5" t="s">
-        <v>68</v>
-      </c>
-      <c r="T5" t="s">
-        <v>104</v>
-      </c>
-      <c r="U5" t="s">
-        <v>71</v>
-      </c>
-      <c r="V5" t="s">
-        <v>72</v>
-      </c>
-      <c r="W5" t="s">
-        <v>73</v>
-      </c>
-      <c r="X5" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>137</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>139</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>140</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>68</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>129</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>101</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>115</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>94</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>141</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:54">
-      <c r="B6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" t="s">
-        <v>60</v>
-      </c>
       <c r="I6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J6" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -2817,183 +2995,213 @@
         <v>6.5</v>
       </c>
       <c r="M6" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="N6" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O6" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="P6" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="Q6" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="R6" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="S6" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="T6" t="s">
+        <v>115</v>
+      </c>
+      <c r="U6" t="s">
+        <v>79</v>
+      </c>
+      <c r="V6" t="s">
+        <v>80</v>
+      </c>
+      <c r="W6">
+        <v>4000</v>
+      </c>
+      <c r="X6" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>157</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>158</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>159</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>160</v>
+      </c>
+      <c r="BC6" t="s">
         <v>104</v>
       </c>
-      <c r="U6" t="s">
-        <v>71</v>
-      </c>
-      <c r="V6" t="s">
-        <v>72</v>
-      </c>
-      <c r="W6" t="s">
-        <v>73</v>
-      </c>
-      <c r="X6" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE6" t="s">
+      <c r="BD6">
+        <v>70000</v>
+      </c>
+      <c r="BE6">
+        <v>25000</v>
+      </c>
+      <c r="BF6">
+        <v>50000</v>
+      </c>
+      <c r="BG6">
+        <v>46</v>
+      </c>
+      <c r="BH6">
+        <v>80000</v>
+      </c>
+      <c r="BI6" t="s">
         <v>105</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="BJ6" t="s">
         <v>106</v>
       </c>
-      <c r="AG6" t="s">
-        <v>145</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>129</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>146</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>147</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>148</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:54">
+      <c r="BK6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:63">
       <c r="B7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:54">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:63">
       <c r="B8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="9" spans="1:54">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:63">
       <c r="B9" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="10" spans="1:54">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:63">
       <c r="B10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="11" spans="1:54">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:63">
       <c r="B11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:54">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:63">
       <c r="B12" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:54">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:63">
       <c r="B13" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="14" spans="1:54">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:63">
       <c r="B14" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="15" spans="1:54">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:63">
       <c r="B15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" spans="1:54">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:63">
       <c r="B16" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:BK16">
+    <sortCondition ref="M2"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3010,21 +3218,21 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="C1" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -3032,10 +3240,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -3043,10 +3251,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -3054,10 +3262,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -3065,10 +3273,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -3091,22 +3299,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B1" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C1" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="F1" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -3131,122 +3339,122 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B1" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="C1" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="E2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="F2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="F3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B4" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C4" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D4" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F4" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="D5" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="F5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B6" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C6" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D6" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="E6" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="F6" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -3270,24 +3478,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C1" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D1" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="E1" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B2">
         <v>46</v>
@@ -3299,12 +3507,12 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B3">
         <v>18</v>
@@ -3316,12 +3524,12 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3333,12 +3541,12 @@
         <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3355,7 +3563,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="B6">
         <v>20</v>
@@ -3367,7 +3575,7 @@
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3390,58 +3598,58 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="B1" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="C1" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="D1" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B4" t="s">
         <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D4" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
